--- a/tabla_cuentas.xlsx
+++ b/tabla_cuentas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian Ortiz\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{851C23E8-6770-4024-A93D-E3FE91457854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F161EEE-C22E-4B8E-BFDD-8E653D2B4693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{23481ECF-5095-433D-A88D-F8772A732E35}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>palabra</t>
   </si>
@@ -71,6 +71,24 @@
   </si>
   <si>
     <t>BICICLETA</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>gasto</t>
+  </si>
+  <si>
+    <t>servicio</t>
+  </si>
+  <si>
+    <t>inventario</t>
+  </si>
+  <si>
+    <t>Activo fijo</t>
+  </si>
+  <si>
+    <t>compras</t>
   </si>
 </sst>
 </file>
@@ -436,97 +454,130 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD275E9-23E6-4FAF-A66C-019F22D3F420}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.54296875" customWidth="1"/>
+    <col min="2" max="2" width="21.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2">
+      <c r="C2" s="2">
         <v>5135</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2">
+      <c r="C3" s="2">
         <v>5135</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2">
+      <c r="C4" s="2">
         <v>5135</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2">
+      <c r="C5" s="2">
         <v>5195</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2">
+      <c r="C6" s="2">
         <v>1435</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="2">
+      <c r="C7" s="2">
         <v>1528</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2">
         <v>5110</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="2">
+      <c r="C9" s="2">
         <v>5195</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2">
+      <c r="C10" s="2">
         <v>5195</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2">
+      <c r="C11" s="2">
         <v>1520</v>
       </c>
     </row>
